--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -1,36 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30_Plzeňský-KV" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NOTES1" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SYSTEM" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="10_liga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20_1liga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="30_2liga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="KVAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="30PRAH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="30STRC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="30JHCK" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="30_Plzeňský-KV" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="30KVRY" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="30USTE" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="30LIBE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="30HRAD" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="30PARD" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="30VYSO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="30JHMR" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="30SVMR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="NOTES" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="NOTES1" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="SYSTEM" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="SERIES" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="CLUBS" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="META" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="TODO" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TODO'!$A$1:$F$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -38,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +78,11 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -84,11 +96,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14283,7 +14301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14332,6 +14350,23 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>H</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0033</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -14404,7 +14439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K255"/>
+  <dimension ref="A1:L255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14463,6 +14498,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14500,6 +14540,11 @@
           <t>14 týmů (4-col): základ + předkolo/QF/SF/finále + Play Out + baráž. Mistr: HC Oceláři Třinec.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14537,6 +14582,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14574,6 +14624,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14611,6 +14666,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14648,6 +14708,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14685,6 +14750,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14722,6 +14792,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14759,6 +14834,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14796,6 +14876,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14833,6 +14918,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14870,6 +14960,11 @@
           <t>1.liga: základ + QF/SF + Play out + baráž.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14907,6 +15002,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14944,6 +15044,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14981,6 +15086,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15018,6 +15128,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15055,6 +15170,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15092,6 +15212,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15166,6 +15291,11 @@
           <t>II.liga: skupiny + QF/SF/finále + baráž o 2.ligu.</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15203,6 +15333,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0020</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15240,6 +15375,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0021</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15277,6 +15417,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15314,6 +15459,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0023</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15351,6 +15501,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0024</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15388,6 +15543,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15425,6 +15585,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15462,6 +15627,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0027</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15499,6 +15669,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0028</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15536,6 +15711,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0029</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15573,6 +15753,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0030</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15679,6 +15864,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0031</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15716,6 +15906,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0032</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15896,6 +16091,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0035</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15933,6 +16133,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0036</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16261,6 +16466,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0038</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16890,6 +17100,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0055</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -16927,6 +17142,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0056</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17255,6 +17475,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0057</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -19100,6 +19325,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0095</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -19280,6 +19510,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0099</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -19719,6 +19954,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0118</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -19830,6 +20070,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0168</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -20084,6 +20329,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0126</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -20454,6 +20704,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0136</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -20671,6 +20926,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0141</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -21295,6 +21555,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0160</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -21480,6 +21745,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0165</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -21591,6 +21861,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0168</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -22474,6 +22749,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0191</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -22876,6 +23156,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0202</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -23350,6 +23635,11 @@
       <c r="J243" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>NODE_S2017_18_0215</t>
         </is>
       </c>
     </row>
@@ -40288,6 +40578,81 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0033</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -32958,6 +32958,11 @@
           <t>SK VELC Žilina</t>
         </is>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0101</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
           <t>30_Středočeský</t>
@@ -36073,6 +36078,11 @@
       <c r="C163" t="inlineStr">
         <is>
           <t>HC KLAUS Timber</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>CLUB_S2017_18_0156</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -14439,7 +14439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L255"/>
+  <dimension ref="A1:N255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14501,6 +14501,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -14587,6 +14587,16 @@
           <t>NODE_S2018_19_0001</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0004</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0009</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14596,6 +14606,14 @@
         <is>
           <t>NODE_S2017_18_0002</t>
         </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -14671,6 +14689,16 @@
           <t>NODE_S2018_19_0003</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0005</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0009</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14680,6 +14708,14 @@
         <is>
           <t>NODE_S2017_18_0004</t>
         </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -14713,6 +14749,12 @@
           <t>NODE_S2018_19_0003</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0006</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14722,6 +14764,14 @@
         <is>
           <t>NODE_S2017_18_0005</t>
         </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -14755,6 +14805,16 @@
           <t>NODE_S2018_19_0003</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0007</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14764,6 +14824,14 @@
         <is>
           <t>NODE_S2017_18_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -14797,6 +14865,8 @@
           <t>NODE_S2018_19_0003</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14806,6 +14876,14 @@
         <is>
           <t>NODE_S2017_18_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -14839,6 +14917,8 @@
           <t>NODE_S2018_19_0003</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14848,6 +14928,14 @@
         <is>
           <t>NODE_S2017_18_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -14881,6 +14969,8 @@
           <t>NODE_S2018_19_0001</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14890,6 +14980,14 @@
         <is>
           <t>NODE_S2017_18_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -15007,6 +15105,16 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0013</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0017</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15016,6 +15124,14 @@
         <is>
           <t>NODE_S2017_18_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>15 týmů</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -15049,6 +15165,16 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0014</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0017</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15058,6 +15184,14 @@
         <is>
           <t>NODE_S2017_18_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -15091,6 +15225,12 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0015</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15100,6 +15240,14 @@
         <is>
           <t>NODE_S2017_18_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -15133,6 +15281,12 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0016</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15142,6 +15296,14 @@
         <is>
           <t>NODE_S2017_18_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -15175,6 +15337,8 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15184,6 +15348,14 @@
         <is>
           <t>NODE_S2017_18_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -15217,6 +15389,8 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15226,6 +15400,14 @@
         <is>
           <t>NODE_S2017_18_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -15506,6 +15688,12 @@
           <t>NODE_S2018_19_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0025</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15515,6 +15703,14 @@
         <is>
           <t>NODE_S2017_18_0024</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>horní část ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -15548,6 +15744,12 @@
           <t>NODE_S2018_19_0019</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15557,6 +15759,14 @@
         <is>
           <t>NODE_S2017_18_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -15590,6 +15800,12 @@
           <t>NODE_S2018_19_0019</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0027</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15599,6 +15815,14 @@
         <is>
           <t>NODE_S2017_18_0026</t>
         </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -15632,6 +15856,8 @@
           <t>NODE_S2018_19_0019</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15641,6 +15867,14 @@
         <is>
           <t>NODE_S2017_18_0027</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -15674,6 +15908,8 @@
           <t>NODE_S2018_19_0019</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15683,6 +15919,14 @@
         <is>
           <t>NODE_S2017_18_0028</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -16180,10 +16424,24 @@
           <t>NODE_S2018_19_0039</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0042</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -16217,10 +16475,28 @@
           <t>NODE_S2018_19_0039</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0047</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0045</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -16328,10 +16604,20 @@
           <t>NODE_S2018_19_0039</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -16402,10 +16688,20 @@
           <t>NODE_S2018_19_0039</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -16624,10 +16920,24 @@
           <t>NODE_S2018_19_0049</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0058</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -16809,10 +17119,24 @@
           <t>NODE_S2018_19_0049</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0061</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -16920,10 +17244,20 @@
           <t>NODE_S2018_19_0049</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -17189,10 +17523,24 @@
           <t>NODE_S2018_19_0049</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0058</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -17374,10 +17722,24 @@
           <t>NODE_S2018_19_0049</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0061</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -17559,10 +17921,24 @@
           <t>NODE_S2018_19_0076</t>
         </is>
       </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0079</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>13 týmů</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -17596,10 +17972,24 @@
           <t>NODE_S2018_19_0076</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0084</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="81">
@@ -17781,10 +18171,24 @@
           <t>NODE_S2018_19_0076</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0087</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="86">
@@ -17892,10 +18296,20 @@
           <t>NODE_S2018_19_0076</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -18368,10 +18782,24 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0111</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -18553,10 +18981,20 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -18664,10 +19102,24 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0111</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="110">
@@ -18775,10 +19227,20 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="113">
@@ -18923,10 +19385,24 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0100</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="117">
@@ -19108,10 +19584,24 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0111</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="122">
@@ -19219,10 +19709,20 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -19594,10 +20094,24 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0134</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N134" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -19631,10 +20145,28 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0141</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0139</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="136">
@@ -19742,10 +20274,20 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="139">
@@ -19816,10 +20358,20 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="141">
@@ -19890,10 +20442,20 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="143">
@@ -20038,10 +20600,24 @@
           <t>NODE_S2018_19_0143</t>
         </is>
       </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0146</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>6 týmů</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="147">
@@ -20075,6 +20651,12 @@
           <t>NODE_S2018_19_0143</t>
         </is>
       </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0148</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20084,6 +20666,14 @@
         <is>
           <t>NODE_S2017_18_0168</t>
         </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -20154,10 +20744,24 @@
           <t>NODE_S2018_19_0143</t>
         </is>
       </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0151</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="150">
@@ -20265,10 +20869,20 @@
           <t>NODE_S2018_19_0143</t>
         </is>
       </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="153">
@@ -20413,10 +21027,24 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0156</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -20450,10 +21078,28 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0161</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0159</t>
+        </is>
+      </c>
       <c r="J157" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -20561,10 +21207,20 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="161">
@@ -20635,10 +21291,20 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="163">
@@ -20751,10 +21417,24 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0156</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -20788,10 +21468,20 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="167">
@@ -20862,10 +21552,20 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N168" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="169">
@@ -21010,10 +21710,24 @@
           <t>NODE_S2018_19_0169</t>
         </is>
       </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0174</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -21121,10 +21835,24 @@
           <t>NODE_S2018_19_0169</t>
         </is>
       </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0179</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N175" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -21306,10 +22034,28 @@
           <t>NODE_S2018_19_0169</t>
         </is>
       </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0184</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0182</t>
+        </is>
+      </c>
       <c r="J180" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="181">
@@ -21417,10 +22163,20 @@
           <t>NODE_S2018_19_0169</t>
         </is>
       </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="184">
@@ -21491,10 +22247,20 @@
           <t>NODE_S2018_19_0169</t>
         </is>
       </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="186">
@@ -21639,10 +22405,24 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0194</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -21866,6 +22646,12 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0205</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21875,6 +22661,14 @@
         <is>
           <t>NODE_S2017_18_0168</t>
         </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="196">
@@ -21982,10 +22776,28 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0202</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0200</t>
+        </is>
+      </c>
       <c r="J198" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="199">
@@ -22093,10 +22905,20 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="202">
@@ -22167,10 +22989,20 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="204">
@@ -22278,10 +23110,24 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0197</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>horní ZČ + postupující z předkola</t>
+        </is>
+      </c>
+      <c r="N206" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="207">
@@ -22463,10 +23309,28 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0202</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0200</t>
+        </is>
+      </c>
       <c r="J211" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N211" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="212">
@@ -22574,10 +23438,20 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N214" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="215">
@@ -22648,10 +23522,20 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N216" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="217">
@@ -22870,10 +23754,24 @@
           <t>NODE_S2018_19_0218</t>
         </is>
       </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0222</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>5 týmů</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -22907,10 +23805,28 @@
           <t>NODE_S2018_19_0218</t>
         </is>
       </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0227</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0225</t>
+        </is>
+      </c>
       <c r="J223" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="224">
@@ -23018,10 +23934,20 @@
           <t>NODE_S2018_19_0218</t>
         </is>
       </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="227">
@@ -23092,10 +24018,20 @@
           <t>NODE_S2018_19_0218</t>
         </is>
       </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="229">
@@ -23240,10 +24176,24 @@
           <t>NODE_S2018_19_0229</t>
         </is>
       </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0232</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>14 týmů</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -23277,10 +24227,24 @@
           <t>NODE_S2018_19_0229</t>
         </is>
       </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0237</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="234">
@@ -23462,10 +24426,24 @@
           <t>NODE_S2018_19_0229</t>
         </is>
       </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0240</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="239">
@@ -23573,10 +24551,20 @@
           <t>NODE_S2018_19_0229</t>
         </is>
       </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="242">
@@ -23721,10 +24709,24 @@
           <t>NODE_S2018_19_0242</t>
         </is>
       </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0245</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -23758,10 +24760,24 @@
           <t>NODE_S2018_19_0242</t>
         </is>
       </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0250</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="247">
@@ -23943,10 +24959,24 @@
           <t>NODE_S2018_19_0242</t>
         </is>
       </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0253</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N251" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="252">
@@ -24054,10 +25084,20 @@
           <t>NODE_S2018_19_0242</t>
         </is>
       </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="255">

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -825,6 +825,11 @@
           <t>HC Oceláři Třinec</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>52</v>
       </c>
@@ -14754,7 +14759,6 @@
           <t>NODE_S2018_19_0006</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14865,8 +14869,6 @@
           <t>NODE_S2018_19_0003</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14917,8 +14919,6 @@
           <t>NODE_S2018_19_0003</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>complete</t>
@@ -14969,8 +14969,6 @@
           <t>NODE_S2018_19_0001</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15230,7 +15228,6 @@
           <t>NODE_S2018_19_0015</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15286,7 +15283,6 @@
           <t>NODE_S2018_19_0016</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15337,8 +15333,6 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15389,8 +15383,6 @@
           <t>NODE_S2018_19_0011</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15693,7 +15685,6 @@
           <t>NODE_S2018_19_0025</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15749,7 +15740,6 @@
           <t>NODE_S2018_19_0026</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15805,7 +15795,6 @@
           <t>NODE_S2018_19_0027</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15856,8 +15845,6 @@
           <t>NODE_S2018_19_0019</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>complete</t>
@@ -15908,8 +15895,6 @@
           <t>NODE_S2018_19_0019</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16429,7 +16414,6 @@
           <t>NODE_S2018_19_0042</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16604,8 +16588,6 @@
           <t>NODE_S2018_19_0039</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16688,8 +16670,6 @@
           <t>NODE_S2018_19_0039</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>complete</t>
@@ -16925,7 +16905,6 @@
           <t>NODE_S2018_19_0058</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17124,7 +17103,6 @@
           <t>NODE_S2018_19_0061</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17244,8 +17222,6 @@
           <t>NODE_S2018_19_0049</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17528,7 +17504,6 @@
           <t>NODE_S2018_19_0058</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17727,7 +17702,6 @@
           <t>NODE_S2018_19_0061</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17926,7 +17900,6 @@
           <t>NODE_S2018_19_0079</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>complete</t>
@@ -17977,7 +17950,6 @@
           <t>NODE_S2018_19_0084</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18176,7 +18148,6 @@
           <t>NODE_S2018_19_0087</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18296,8 +18267,6 @@
           <t>NODE_S2018_19_0076</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18787,7 +18756,6 @@
           <t>NODE_S2018_19_0111</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
           <t>complete</t>
@@ -18981,8 +18949,6 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="J106" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19107,7 +19073,6 @@
           <t>NODE_S2018_19_0111</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="J109" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19227,8 +19192,6 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19390,7 +19353,6 @@
           <t>NODE_S2018_19_0100</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19589,7 +19551,6 @@
           <t>NODE_S2018_19_0111</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="J121" t="inlineStr">
         <is>
           <t>complete</t>
@@ -19709,8 +19670,6 @@
           <t>NODE_S2018_19_0089</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20099,7 +20058,6 @@
           <t>NODE_S2018_19_0134</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20274,8 +20232,6 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20358,8 +20314,6 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20442,8 +20396,6 @@
           <t>NODE_S2018_19_0131</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20605,7 +20557,6 @@
           <t>NODE_S2018_19_0146</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20656,7 +20607,6 @@
           <t>NODE_S2018_19_0148</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20749,7 +20699,6 @@
           <t>NODE_S2018_19_0151</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>complete</t>
@@ -20869,8 +20818,6 @@
           <t>NODE_S2018_19_0143</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21032,7 +20979,6 @@
           <t>NODE_S2018_19_0156</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21207,8 +21153,6 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21291,8 +21235,6 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21422,7 +21364,6 @@
           <t>NODE_S2018_19_0156</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21468,8 +21409,6 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21552,8 +21491,6 @@
           <t>NODE_S2018_19_0153</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21715,7 +21652,6 @@
           <t>NODE_S2018_19_0174</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
           <t>complete</t>
@@ -21840,7 +21776,6 @@
           <t>NODE_S2018_19_0179</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22163,8 +22098,6 @@
           <t>NODE_S2018_19_0169</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22247,8 +22180,6 @@
           <t>NODE_S2018_19_0169</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22410,7 +22341,6 @@
           <t>NODE_S2018_19_0194</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22651,7 +22581,6 @@
           <t>NODE_S2018_19_0205</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22905,8 +22834,6 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>complete</t>
@@ -22989,8 +22916,6 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23115,7 +23040,6 @@
           <t>NODE_S2018_19_0197</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23438,8 +23362,6 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23522,8 +23444,6 @@
           <t>NODE_S2018_19_0186</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23759,7 +23679,6 @@
           <t>NODE_S2018_19_0222</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>complete</t>
@@ -23934,8 +23853,6 @@
           <t>NODE_S2018_19_0218</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr"/>
-      <c r="H226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24018,8 +23935,6 @@
           <t>NODE_S2018_19_0218</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24181,7 +24096,6 @@
           <t>NODE_S2018_19_0232</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24232,7 +24146,6 @@
           <t>NODE_S2018_19_0237</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24431,7 +24344,6 @@
           <t>NODE_S2018_19_0240</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24551,8 +24463,6 @@
           <t>NODE_S2018_19_0229</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24714,7 +24624,6 @@
           <t>NODE_S2018_19_0245</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24765,7 +24674,6 @@
           <t>NODE_S2018_19_0250</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>complete</t>
@@ -24964,7 +24872,6 @@
           <t>NODE_S2018_19_0253</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>complete</t>
@@ -25084,8 +24991,6 @@
           <t>NODE_S2018_19_0242</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>complete</t>
@@ -41558,7 +41463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41630,6 +41535,18 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>2 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HC Oceláři Třinec</t>
         </is>
       </c>
     </row>

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -3820,7 +3820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W27"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5354,6 +5354,73 @@
       <c r="U27" s="2" t="n"/>
       <c r="V27" s="2" t="n"/>
       <c r="W27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0256</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0256</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7621,7 +7688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10441,6 +10508,118 @@
       <c r="V52" s="2" t="n"/>
       <c r="W52" s="2" t="n"/>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>4</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00258</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>7</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00259</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10452,7 +10631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11355,6 +11534,362 @@
       <c r="U16" s="2" t="n"/>
       <c r="V16" s="2" t="n"/>
       <c r="W16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>soutěž nehrána</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0260</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00260</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0261</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00261</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0262</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00262</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0263</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00263</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0264</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00264</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0265</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00265</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>5</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jihlava</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0266</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00266</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14444,7 +14979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N255"/>
+  <dimension ref="A1:N260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25039,6 +25574,191 @@
       <c r="J255" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Středočeský – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>REG_STC</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0049</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>REG_LBK</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0153</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>REG_PAK</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0186</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0218</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Vysočina – Jihlava</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>league</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>REG_VYS</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0218</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Okresní soutěž – základ úplnosti z clbs (jen názvy).</t>
         </is>
       </c>
     </row>
@@ -29354,7 +30074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J256"/>
+  <dimension ref="A1:J267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -41449,6 +42169,303 @@
       <c r="J256" t="inlineStr">
         <is>
           <t>Nový Jičín</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TJ Božetice</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>TJ Božetice</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>30STRC</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>HC TS Varnsdorf</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>30LIBE</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>HC Světlá nad Sázavou</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>HC Chotěboř</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>30PARD</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>soutěž nehrána</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>soutěž nehrána</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>HC Zastávka</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>HAS Jihlava</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>HC Chvojkovice – Brod</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HC Amatero Luka nad Jihlavou</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>HC Velký Beranov</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>HC Kokodáci</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>30VYSO</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>L40</t>
         </is>
       </c>
     </row>
@@ -46079,7 +47096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W63"/>
+  <dimension ref="A1:W65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -49895,6 +50912,73 @@
       <c r="U63" s="2" t="n"/>
       <c r="V63" s="2" t="n"/>
       <c r="W63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0255</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TJ Božetice</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>:</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Krajská liga</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0255</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>L40</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>CLUB_S2018_19_0256</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>TR_S2018_19_00256</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -41,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -60,8 +60,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -83,6 +87,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -96,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +116,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -42578,7 +42589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -42635,11 +42646,115 @@
           <t>NODE_S2018_19_0033</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL L35'</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Středočeský – Krajská liga (Středočeský kraj) · NODE_S2018_19_0255</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (TJ Božetice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2018_19_0256</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 1 tým (HC TS Varnsdorf), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Pardubický – Krajská liga (Pardubický kraj) · NODE_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (HC Světlá nad Sázavou, HC Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Vysočina – Krajská liga (Vysočina) · NODE_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>máme jen 2 týmy (soutěž nehrána, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F2"/>

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14852,7 +14855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14916,6 +14919,74 @@
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0255</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (TJ Božetice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0256</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 1 tým (HC TS Varnsdorf), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0257</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (HC Světlá nad Sázavou, HC Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S2018_19_0258</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen 2 týmy (soutěž nehrána, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -42666,7 +42737,7 @@
           <t>Středočeský – Krajská liga (Středočeský kraj) · NODE_S2018_19_0255</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (TJ Božetice), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -42692,7 +42763,7 @@
           <t>Liberecký – Krajská liga (Liberecký kraj) · NODE_S2018_19_0256</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>máme jen 1 tým (HC TS Varnsdorf), chybí zbytek týmů i celá tabulka  [torzo-audit]</t>
         </is>
@@ -42718,7 +42789,7 @@
           <t>Pardubický – Krajská liga (Pardubický kraj) · NODE_S2018_19_0257</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (HC Světlá nad Sázavou, HC Chotěboř), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>
@@ -42744,7 +42815,7 @@
           <t>Vysočina – Krajská liga (Vysočina) · NODE_S2018_19_0258</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>máme jen 2 týmy (soutěž nehrána, HC Zastávka), chybí zbytek týmů a tabulka  [torzo-audit]</t>
         </is>

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -16924,7 +16924,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hvězda Praha – SK Žižkov  8:1,7:3</t>
+          <t>Hvězda Praha – SK Žižkov 8:1,7:3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HC TNP Praha  - HC Kobra Praha "B"  12:1,5:1</t>
+          <t>HC TNP Praha - HC Kobra Praha "B" 12:1,5:1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -17227,7 +17227,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HC Kobra Praha "B" – SK Žižkov  4:5,3:4 PP</t>
+          <t>HC Kobra Praha "B" – SK Žižkov 4:5,3:4 PP</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hvězda Praha – HC TNP Praha  1:4,5:4,4:10</t>
+          <t>Hvězda Praha – HC TNP Praha 1:4,5:4,4:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -17346,7 +17346,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -17544,7 +17544,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SK Černošice – HK Lev Slaný  6:4,9:4</t>
+          <t>SK Černošice – HK Lev Slaný 6:4,9:4</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>HC Junior Mělník – HC Rakovník  5:3,8:2</t>
+          <t>HC Junior Mělník – HC Rakovník 5:3,8:2</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -17618,7 +17618,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>HK Čáslav – Slavoj Velké Popovice  7:0,4:3</t>
+          <t>HK Čáslav – Slavoj Velké Popovice 7:0,4:3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -17655,7 +17655,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HC Poděbrady – HC Lev Benešov  3:4,5:2,7:4</t>
+          <t>HC Poděbrady – HC Lev Benešov 3:4,5:2,7:4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -17742,7 +17742,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SK Černošice – HC Poděbrady  8:3,4:0</t>
+          <t>SK Černošice – HC Poděbrady 8:3,4:0</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -17779,7 +17779,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>HK Čáslav – HC Junior Mělník  4:0,2:3 PP,5:3</t>
+          <t>HK Čáslav – HC Junior Mělník 4:0,2:3 PP,5:3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HK Příbram 99 – HC Benátky nad Jizerou  "B" 3:4, 3:5</t>
+          <t>HK Příbram 99 – HC Benátky nad Jizerou "B" 3:4, 3:5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -18415,7 +18415,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Slavoj Český Krumlov – HC Vajgar Jindřichův Hradec  2:4,3:4</t>
+          <t>Slavoj Český Krumlov – HC Vajgar Jindřichův Hradec 2:4,3:4</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>HC Strakonice – HC Vimperk  4:3 PP,3:4 SN,5:4 PP</t>
+          <t>HC Strakonice – HC Vimperk 4:3 PP,3:4 SN,5:4 PP</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TJ Hluboká nad Vltavou – HC Milevsko 2010  8:5,1:3,6:3</t>
+          <t>TJ Hluboká nad Vltavou – HC Milevsko 2010 8:5,1:3,6:3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -18787,7 +18787,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HC Strakonice - HC Vajgar Jindřichův Hradec  2:3 PP,2:3</t>
+          <t>HC Strakonice - HC Vajgar Jindřichův Hradec 2:3 PP,2:3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TJ Lokomotiva Veselí nad Lužnicí – TJ Hluboká nad Vltavou  5:4,5:0 K</t>
+          <t>TJ Lokomotiva Veselí nad Lužnicí – TJ Hluboká nad Vltavou 5:4,5:0 K</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -18943,7 +18943,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Plzeňský-KV L40</t>
+          <t>Plzeňský-KV, 4. úroveň</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>HC Pubec Plzeň  - HC Saxana Group  1:2, 5:0 K, 8:4</t>
+          <t>HC Pubec Plzeň - HC Saxana Group 1:2, 5:0 K, 8:4</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HC Chotíkov „A“  - Sokol Horní Lukavice 2:7, 3:10</t>
+          <t>HC Chotíkov „A“ - Sokol Horní Lukavice 2:7, 3:10</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -20309,7 +20309,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sokol Horní Lukavice – DTJ Klabava  4:2, 3:5, nájezdy 0:1</t>
+          <t>Sokol Horní Lukavice – DTJ Klabava 4:2, 3:5, nájezdy 0:1</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -20573,7 +20573,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>30_Karlovarský L40</t>
+          <t>Karlovarský, 4. úroveň</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -20752,7 +20752,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HC Mariánské Lázně B  - IHT Brimstones Cheb  5:0 K,12:2</t>
+          <t>HC Mariánské Lázně B - IHT Brimstones Cheb 5:0 K,12:2</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -20789,7 +20789,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>HC PSK 96 Cheb  - Stadion Cheb "B"  5:0 K,2:4,0:5 K</t>
+          <t>HC PSK 96 Cheb - Stadion Cheb "B" 5:0 K,2:4,0:5 K</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -20871,7 +20871,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HC Auta a Auta Cheb  - SK HC MAAN Cheb 5:6 SN,3:4 SN</t>
+          <t>HC Auta a Auta Cheb - SK HC MAAN Cheb 5:6 SN,3:4 SN</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>HC PSK 96 Cheb  - IHT Brimstones Cheb  0:5 K,0:5 K</t>
+          <t>HC PSK 96 Cheb - IHT Brimstones Cheb 0:5 K,0:5 K</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -21035,7 +21035,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HC Mariánské Lázně B  - Stadion Cheb "B"  7:3,4:3</t>
+          <t>HC Mariánské Lázně B - Stadion Cheb "B" 7:3,4:3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -21072,7 +21072,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>30_Ústecký L40</t>
+          <t>Ústecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>HC Roudnice nad Labem -  SK Kadaň "B" 1:4,5:2,8:11</t>
+          <t>HC Roudnice nad Labem - SK Kadaň "B" 1:4,5:2,8:11</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>HC Slovan Louny – SK Kadaň "B"  6:5 SN,4:0</t>
+          <t>HC Slovan Louny – SK Kadaň "B" 6:5 SN,4:0</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -21375,7 +21375,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>HC Tygři Klášterec nad Ohří – HC Stadion Litoměřice "B"  3:2,5:2</t>
+          <t>HC Tygři Klášterec nad Ohří – HC Stadion Litoměřice "B" 3:2,5:2</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>HC Slovan Louny – HC Tygři Klášterec nad Ohří   5:1,4:0</t>
+          <t>HC Slovan Louny – HC Tygři Klášterec nad Ohří 5:1,4:0</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>30_Liberecký L40</t>
+          <t>Liberecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -21673,7 +21673,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>HC Stavební stroje Jičín - HC Lomnice nad Popelkou  2:4,6:0,7:3</t>
+          <t>HC Stavební stroje Jičín - HC Lomnice nad Popelkou 2:4,6:0,7:3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Slavoj Liberec  - HC Turnov 1931  3:6,3:5</t>
+          <t>Slavoj Liberec - HC Turnov 1931 3:6,3:5</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Slavoj Liberec  - HC Lomnice nad Popelkou  4:5,8:4,3:2</t>
+          <t>Slavoj Liberec - HC Lomnice nad Popelkou 4:5,8:4,3:2</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -22048,7 +22048,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HC Lomnice nad Popelkou  - HC Turnov 1931 4:3</t>
+          <t>HC Lomnice nad Popelkou - HC Turnov 1931 4:3</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -22130,7 +22130,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>BK Nová Paka  - HC Stavební stroje Jičín 9:5</t>
+          <t>BK Nová Paka - HC Stavební stroje Jičín 9:5</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>30_Hradecký L40</t>
+          <t>Hradecký, 4. úroveň</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -22415,7 +22415,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BK Nová Paka - TJ Spartak Nové Město nad Metuji  0:5 K,5:2,9:0</t>
+          <t>BK Nová Paka - TJ Spartak Nové Město nad Metuji 0:5 K,5:2,9:0</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov  - SK Třebechovice pod Orebem 8:4,8:4</t>
+          <t>Stadion Nový Bydžov - SK Třebechovice pod Orebem 8:4,8:4</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -22489,7 +22489,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>HC Náchod – HC Trutnov "B"  9:1,3:4 PP,3:2</t>
+          <t>HC Náchod – HC Trutnov "B" 9:1,3:4 PP,3:2</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -22526,7 +22526,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>HC Jaroměř – HC Wikov Hronov  5:2,4:3 PP</t>
+          <t>HC Jaroměř – HC Wikov Hronov 5:2,4:3 PP</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -22618,7 +22618,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>BK Nová Paka -  HC Jaroměř  4:6,6:0,4:2,2:6,6:0</t>
+          <t>BK Nová Paka - HC Jaroměř 4:6,6:0,4:2,2:6,6:0</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Stadion Nový Bydžov – HC Náchod  8:5,5:3,2:3,5:11,6:2</t>
+          <t>Stadion Nový Bydžov – HC Náchod 8:5,5:3,2:3,5:11,6:2</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -22819,7 +22819,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>BK Nová Paka – Stadion Nový Bydžov  6:4,1:4,9:4,8:3</t>
+          <t>BK Nová Paka – Stadion Nový Bydžov 6:4,1:4,9:4,8:3</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>30_Pardubický L40</t>
+          <t>Pardubický, 4. úroveň</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -23225,7 +23225,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>HC Hlinsko – TJ Orli Lanškroun  6:5,5:3</t>
+          <t>HC Hlinsko – TJ Orli Lanškroun 6:5,5:3</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -23262,7 +23262,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>HC Spartak Choceň – HC Skuteč  0:1,3:7</t>
+          <t>HC Spartak Choceň – HC Skuteč 0:1,3:7</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -23354,7 +23354,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou – HC Skuteč  5:3,5:0</t>
+          <t>HC Světlá nad Sázavou – HC Skuteč 5:3,5:0</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -23391,7 +23391,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>HC Litomyšl  - HC Hlinsko  2:6,4:5</t>
+          <t>HC Litomyšl - HC Hlinsko 2:6,4:5</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -23555,7 +23555,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou  - HC Hlinsko  5:6 PP,1:6</t>
+          <t>HC Světlá nad Sázavou - HC Hlinsko 5:6 PP,1:6</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>HC Chrudim – HC Spartak Choceň  7:1,7:1,5:0</t>
+          <t>HC Chrudim – HC Spartak Choceň 7:1,7:1,5:0</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>HC Světlá nad Sázavou – HC Chotěboř  3:4 PP,1:2 SN,3:0,1:3</t>
+          <t>HC Světlá nad Sázavou – HC Chotěboř 3:4 PP,1:2 SN,3:0,1:3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -23753,7 +23753,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová  - HC Hlinsko  6:3,6:4,5:6 PP,6:5</t>
+          <t>Slovan Moravská Třebová - HC Hlinsko 6:3,6:4,5:6 PP,6:5</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -23790,7 +23790,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>HC Litomyšl - HC Kohouti Česká Třebová   3:5,3:12,4:3,2:5</t>
+          <t>HC Litomyšl - HC Kohouti Česká Třebová 3:5,3:12,4:3,2:5</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -23882,7 +23882,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>HC Chrudim – HC Chotěboř  1:2,3:1,4:0,5:3</t>
+          <t>HC Chrudim – HC Chotěboř 1:2,3:1,4:0,5:3</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -23919,7 +23919,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Slovan Moravská Třebová  - HC Kohouti Česká Třebová  6:2,4:5,3:6,9:6,5:6 PP</t>
+          <t>Slovan Moravská Třebová - HC Kohouti Česká Třebová 6:2,4:5,3:6,9:6,5:6 PP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -24001,7 +24001,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>HC Chotěboř - Slovan Moravská Třebová  1:5, 3:7</t>
+          <t>HC Chotěboř - Slovan Moravská Třebová 1:5, 3:7</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -24083,7 +24083,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>HC Chrudim - HC Kohouti Česká Třebová  3:0,1:4,3:7,3:6</t>
+          <t>HC Chrudim - HC Kohouti Česká Třebová 3:0,1:4,3:7,3:6</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>30_Vysočina L40</t>
+          <t>Vysočina, 4. úroveň</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -24373,7 +24373,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>BK Zubři Bystřice nad Pernštejnem  - Náměšť nad Oslavou  3:6, 1:6</t>
+          <t>BK Zubři Bystřice nad Pernštejnem - Náměšť nad Oslavou 3:6, 1:6</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -24492,7 +24492,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HC Zastávka - BK Zubři Bystřice nad Pernštejnem  5:8,3:2 PP,7:5</t>
+          <t>HC Zastávka - BK Zubři Bystřice nad Pernštejnem 5:8,3:2 PP,7:5</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Náměšť nad Oslavou  - HHK Velké Meziříčí "B"  4:0,7:4</t>
+          <t>Náměšť nad Oslavou - HHK Velké Meziříčí "B" 4:0,7:4</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -24611,7 +24611,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -24785,7 +24785,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – Spartak Velká Bíteš  3:1,5:0</t>
+          <t>HHK Velké Meziříčí – Spartak Velká Bíteš 3:1,5:0</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -24822,7 +24822,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>SHKM Hodonín – HC Uničov   4:1,9:3</t>
+          <t>SHKM Hodonín – HC Uničov 4:1,9:3</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -24859,7 +24859,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Hokej Uherský Ostroh – Spartak Uherský Brod  3:1,1:2,4:3</t>
+          <t>Hokej Uherský Ostroh – Spartak Uherský Brod 3:1,1:2,4:3</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -24896,7 +24896,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>SKMB Boskovice – HK Kroměříž  5:4 PP,5:1</t>
+          <t>SKMB Boskovice – HK Kroměříž 5:4 PP,5:1</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -24983,7 +24983,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – SKMB Boskovice  4:2,0:3,4:0,6:7 PP,9:2</t>
+          <t>HHK Velké Meziříčí – SKMB Boskovice 4:2,0:3,4:0,6:7 PP,9:2</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -25020,7 +25020,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>SHKM Hodonín – Hokej Uherský Ostroh  7:4,5:2,6:7 SN,10:4</t>
+          <t>SHKM Hodonín – Hokej Uherský Ostroh 7:4,5:2,6:7 SN,10:4</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -25102,7 +25102,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>HHK Velké Meziříčí – SHKM Hodonín  5:3,5:6,4:3,2:4,4:5</t>
+          <t>HHK Velké Meziříčí – SHKM Hodonín 5:3,5:6,4:3,2:4,4:5</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -25139,7 +25139,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -25313,7 +25313,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>HK Krnov – HC Rožnov pod Radhoštěm  6:2,7:3</t>
+          <t>HK Krnov – HC Rožnov pod Radhoštěm 6:2,7:3</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -25350,7 +25350,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>HC Studénka – TJ Horní Benešov  8:4,4:2</t>
+          <t>HC Studénka – TJ Horní Benešov 8:4,4:2</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -25387,7 +25387,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>HC Wolves Český Těšín – HC Frýdek-Místek  "B"   7:6,5:4</t>
+          <t>HC Wolves Český Těšín – HC Frýdek-Místek "B" 7:6,5:4</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>HC Býci Karviná – HC Bospor Bohumín  6:2,4:3 PP</t>
+          <t>HC Býci Karviná – HC Bospor Bohumín 6:2,4:3 PP</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>HK Krnov – HC Býci Karviná  3:2,1:6,1:2 PP</t>
+          <t>HK Krnov – HC Býci Karviná 3:2,1:6,1:2 PP</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -25548,7 +25548,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>HC Studénka – HC Wolves Český Těšín  0:5,1:4</t>
+          <t>HC Studénka – HC Wolves Český Těšín 0:5,1:4</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>HC Wolves Český Těšín - HC Býci Karviná  7:3,3:2 PP,4:2</t>
+          <t>HC Wolves Český Těšín - HC Býci Karviná 7:3,3:2 PP,4:2</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">

--- a/data/S2018_19_FINAL.xlsx
+++ b/data/S2018_19_FINAL.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -7993,7 +7993,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -8660,7 +8660,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
